--- a/data/raw/isic.xlsx
+++ b/data/raw/isic.xlsx
@@ -1009,7 +1009,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:Z40"/>
+  <dimension ref="A1:Z39"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="10" customWidth="1" style="25" min="1" max="1"/>
@@ -4293,7 +4293,6 @@
         </is>
       </c>
     </row>
-    <row r="40"/>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="N2:W2"/>
@@ -4314,7 +4313,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:Z40"/>
+  <dimension ref="A1:Z39"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="10" customWidth="1" style="25" min="1" max="1"/>
@@ -7598,7 +7597,6 @@
         </is>
       </c>
     </row>
-    <row r="40"/>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="N2:W2"/>
@@ -7619,7 +7617,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P39"/>
+  <dimension ref="A1:P35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" style="26" min="1" max="1"/>
@@ -8751,126 +8749,10 @@
       <c r="O35" s="76" t="n"/>
       <c r="P35" s="69" t="n"/>
     </row>
-    <row r="36" ht="18" customHeight="1" s="26">
-      <c r="A36" s="77" t="inlineStr">
-        <is>
-          <t>M399693</t>
-        </is>
-      </c>
-      <c r="B36" s="77" t="inlineStr">
-        <is>
-          <t>Fassi</t>
-        </is>
-      </c>
-      <c r="C36" s="77" t="inlineStr">
-        <is>
-          <t>Soukaina</t>
-        </is>
-      </c>
-      <c r="D36" s="73" t="n"/>
-      <c r="E36" s="65" t="n"/>
-      <c r="F36" s="65" t="n"/>
-      <c r="G36" s="65" t="n"/>
-      <c r="H36" s="65" t="n"/>
-      <c r="I36" s="65" t="n"/>
-      <c r="J36" s="65" t="n"/>
-      <c r="K36" s="65" t="n"/>
-      <c r="L36" s="74" t="n"/>
-      <c r="M36" s="66" t="n"/>
-      <c r="N36" s="75" t="n"/>
-      <c r="O36" s="76" t="n"/>
-      <c r="P36" s="69" t="n"/>
-    </row>
-    <row r="37" ht="18" customHeight="1" s="26">
-      <c r="A37" s="63" t="inlineStr">
-        <is>
-          <t>T841665</t>
-        </is>
-      </c>
-      <c r="B37" s="63" t="inlineStr">
-        <is>
-          <t>Ghali</t>
-        </is>
-      </c>
-      <c r="C37" s="63" t="inlineStr">
-        <is>
-          <t>Anas</t>
-        </is>
-      </c>
-      <c r="D37" s="73" t="n"/>
-      <c r="E37" s="65" t="n"/>
-      <c r="F37" s="65" t="n"/>
-      <c r="G37" s="65" t="n"/>
-      <c r="H37" s="65" t="n"/>
-      <c r="I37" s="65" t="n"/>
-      <c r="J37" s="65" t="n"/>
-      <c r="K37" s="65" t="n"/>
-      <c r="L37" s="74" t="n"/>
-      <c r="M37" s="66" t="n"/>
-      <c r="N37" s="75" t="n"/>
-      <c r="O37" s="76" t="n"/>
-      <c r="P37" s="69" t="n"/>
-    </row>
-    <row r="38" ht="18" customHeight="1" s="26">
-      <c r="A38" s="77" t="inlineStr">
-        <is>
-          <t>R555717</t>
-        </is>
-      </c>
-      <c r="B38" s="77" t="inlineStr">
-        <is>
-          <t>Harrak</t>
-        </is>
-      </c>
-      <c r="C38" s="77" t="inlineStr">
-        <is>
-          <t>Zineb</t>
-        </is>
-      </c>
-      <c r="D38" s="73" t="n"/>
-      <c r="E38" s="65" t="n"/>
-      <c r="F38" s="65" t="n"/>
-      <c r="G38" s="65" t="n"/>
-      <c r="H38" s="65" t="n"/>
-      <c r="I38" s="65" t="n"/>
-      <c r="J38" s="65" t="n"/>
-      <c r="K38" s="65" t="n"/>
-      <c r="L38" s="74" t="n"/>
-      <c r="M38" s="66" t="n"/>
-      <c r="N38" s="75" t="n"/>
-      <c r="O38" s="76" t="n"/>
-      <c r="P38" s="69" t="n"/>
-    </row>
-    <row r="39" ht="18" customHeight="1" s="26">
-      <c r="A39" s="63" t="inlineStr">
-        <is>
-          <t>T636960</t>
-        </is>
-      </c>
-      <c r="B39" s="63" t="inlineStr">
-        <is>
-          <t>Idmansour</t>
-        </is>
-      </c>
-      <c r="C39" s="63" t="inlineStr">
-        <is>
-          <t>Nabil</t>
-        </is>
-      </c>
-      <c r="D39" s="73" t="n"/>
-      <c r="E39" s="65" t="n"/>
-      <c r="F39" s="65" t="n"/>
-      <c r="G39" s="65" t="n"/>
-      <c r="H39" s="65" t="n"/>
-      <c r="I39" s="65" t="n"/>
-      <c r="J39" s="65" t="n"/>
-      <c r="K39" s="65" t="n"/>
-      <c r="L39" s="74" t="n"/>
-      <c r="M39" s="66" t="n"/>
-      <c r="N39" s="75" t="n"/>
-      <c r="O39" s="76" t="n"/>
-      <c r="P39" s="69" t="n"/>
-    </row>
+    <row r="36" ht="18" customHeight="1" s="26"/>
+    <row r="37" ht="18" customHeight="1" s="26"/>
+    <row r="38" ht="18" customHeight="1" s="26"/>
+    <row r="39" ht="18" customHeight="1" s="26"/>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="D2:M2"/>

--- a/data/raw/isic.xlsx
+++ b/data/raw/isic.xlsx
@@ -1338,68 +1338,68 @@
         <v>0</v>
       </c>
       <c r="E5" s="43" t="n">
-        <v>12.8</v>
+        <v>8.91</v>
       </c>
       <c r="F5" s="43" t="n">
-        <v>14.79</v>
+        <v>10.13</v>
       </c>
       <c r="G5" s="44" t="n">
-        <v>11.86</v>
+        <v>10.04</v>
       </c>
       <c r="H5" s="44" t="n">
-        <v>11.34</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="I5" s="43" t="n">
-        <v>15.59</v>
+        <v>10.95</v>
       </c>
       <c r="J5" s="43" t="n">
-        <v>13.49</v>
+        <v>11.46</v>
       </c>
       <c r="K5" s="43" t="n">
-        <v>14.14</v>
+        <v>11.92</v>
       </c>
       <c r="M5" s="66" t="n">
-        <v>13.37</v>
+        <v>10.28</v>
       </c>
       <c r="N5" s="42" t="n">
         <v>14</v>
       </c>
       <c r="O5" s="44" t="n">
-        <v>11.2</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="P5" s="43" t="n">
-        <v>12.95</v>
+        <v>10.7</v>
       </c>
       <c r="Q5" s="43" t="n">
-        <v>14.87</v>
+        <v>10.23</v>
       </c>
       <c r="R5" s="43" t="n">
-        <v>19</v>
+        <v>13.41</v>
       </c>
       <c r="S5" s="43" t="n">
-        <v>16.99</v>
+        <v>13.42</v>
       </c>
       <c r="T5" s="43" t="n">
-        <v>18.58</v>
+        <v>15.22</v>
       </c>
       <c r="U5" s="43" t="n">
-        <v>17.27</v>
+        <v>14.18</v>
       </c>
       <c r="V5" s="43" t="n">
-        <v>13.03</v>
+        <v>9.52</v>
       </c>
       <c r="W5" s="66" t="n">
-        <v>15.05</v>
+        <v>11.9</v>
       </c>
       <c r="X5" s="68" t="n">
-        <v>14.21</v>
+        <v>11.09</v>
       </c>
       <c r="Y5" s="61" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Z5" s="78" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
     </row>
@@ -1933,68 +1933,68 @@
         <v>13</v>
       </c>
       <c r="E12" s="43" t="n">
-        <v>14.2</v>
+        <v>11.75</v>
       </c>
       <c r="F12" s="44" t="n">
-        <v>11.91</v>
+        <v>9.77</v>
       </c>
       <c r="G12" s="43" t="n">
-        <v>14.9</v>
+        <v>12.47</v>
       </c>
       <c r="H12" s="43" t="n">
-        <v>13.15</v>
+        <v>10.61</v>
       </c>
       <c r="I12" s="43" t="n">
-        <v>14.45</v>
+        <v>11.33</v>
       </c>
       <c r="J12" s="43" t="n">
-        <v>12.15</v>
+        <v>9.31</v>
       </c>
       <c r="K12" s="43" t="n">
-        <v>14.7</v>
+        <v>10.65</v>
       </c>
       <c r="M12" s="66" t="n">
-        <v>13.66</v>
+        <v>10.84</v>
       </c>
       <c r="N12" s="42" t="n">
         <v>5</v>
       </c>
       <c r="O12" s="43" t="n">
-        <v>14.84</v>
+        <v>12.44</v>
       </c>
       <c r="P12" s="43" t="n">
-        <v>12.75</v>
+        <v>10.77</v>
       </c>
       <c r="Q12" s="44" t="n">
-        <v>11.95</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="R12" s="44" t="n">
-        <v>10.73</v>
+        <v>7.63</v>
       </c>
       <c r="S12" s="43" t="n">
-        <v>14.42</v>
+        <v>10.77</v>
       </c>
       <c r="T12" s="43" t="n">
-        <v>18.6</v>
+        <v>13.76</v>
       </c>
       <c r="U12" s="43" t="n">
-        <v>15.17</v>
+        <v>12.88</v>
       </c>
       <c r="V12" s="43" t="n">
-        <v>17.48</v>
+        <v>11.98</v>
       </c>
       <c r="W12" s="66" t="n">
-        <v>14.32</v>
+        <v>11.08</v>
       </c>
       <c r="X12" s="68" t="n">
-        <v>13.99</v>
+        <v>10.96</v>
       </c>
       <c r="Y12" s="61" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z12" s="78" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
     </row>
@@ -2273,68 +2273,68 @@
         <v>13</v>
       </c>
       <c r="E16" s="43" t="n">
-        <v>12.67</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="F16" s="43" t="n">
-        <v>13.29</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="G16" s="44" t="n">
-        <v>10.28</v>
+        <v>7.05</v>
       </c>
       <c r="H16" s="44" t="n">
-        <v>10.22</v>
+        <v>7.39</v>
       </c>
       <c r="I16" s="44" t="n">
-        <v>8.49</v>
+        <v>6.78</v>
       </c>
       <c r="J16" s="43" t="n">
-        <v>13.96</v>
+        <v>11.09</v>
       </c>
       <c r="K16" s="43" t="n">
-        <v>14.21</v>
+        <v>10.11</v>
       </c>
       <c r="M16" s="66" t="n">
-        <v>11.74</v>
+        <v>8.67</v>
       </c>
       <c r="N16" s="42" t="n">
         <v>14</v>
       </c>
       <c r="O16" s="43" t="n">
-        <v>15.9</v>
+        <v>12.06</v>
       </c>
       <c r="P16" s="43" t="n">
-        <v>14.62</v>
+        <v>10.99</v>
       </c>
       <c r="Q16" s="43" t="n">
-        <v>12.2</v>
+        <v>9.48</v>
       </c>
       <c r="R16" s="43" t="n">
-        <v>15.14</v>
+        <v>10.6</v>
       </c>
       <c r="S16" s="43" t="n">
-        <v>12.54</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="T16" s="43" t="n">
-        <v>13.23</v>
+        <v>11.19</v>
       </c>
       <c r="U16" s="43" t="n">
-        <v>12.53</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="V16" s="43" t="n">
-        <v>17.16</v>
+        <v>14.26</v>
       </c>
       <c r="W16" s="66" t="n">
-        <v>14.34</v>
+        <v>10.95</v>
       </c>
       <c r="X16" s="68" t="n">
-        <v>13.04</v>
+        <v>9.81</v>
       </c>
       <c r="Y16" s="61" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z16" s="78" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
     </row>
